--- a/output/pdf_financials_xlsx/SCM.xlsx
+++ b/output/pdf_financials_xlsx/SCM.xlsx
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.141616</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.141616</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.252392</v>
       </c>
     </row>
     <row r="93">
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-5.4e-05</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0</v>
@@ -3282,7 +3282,11 @@
           <t>Reserve for warrants 12</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -3590,7 +3594,11 @@
           <t>Reserve for warrants 10</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
         <v>0.141616</v>
       </c>
@@ -3677,7 +3685,11 @@
           <t>Recovery of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SCM.xlsx
+++ b/output/pdf_financials_xlsx/SCM.xlsx
@@ -1126,13 +1126,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.218608</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.018745</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.03682</v>
       </c>
     </row>
     <row r="35">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.218608</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.018745</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.168</v>
+        <v>0.20482</v>
       </c>
     </row>
     <row r="37">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/SCM.xlsx
+++ b/output/pdf_financials_xlsx/SCM.xlsx
@@ -1672,13 +1672,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="68">
@@ -2212,10 +2212,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -2230,16 +2228,14 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>-0.042799</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.027763</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.016139</v>
       </c>
     </row>
     <row r="102">
@@ -2248,10 +2244,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -2266,10 +2260,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>-0.002</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>-0.00795</v>
@@ -2284,10 +2276,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.057194</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>0.146929</v>
@@ -2302,10 +2292,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>0</v>
@@ -2320,16 +2308,14 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.012395</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.138979</v>
+        <v>0.166742</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.032458</v>
+        <v>-0.016319</v>
       </c>
     </row>
     <row r="107">
@@ -2338,10 +2324,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.103329</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0</v>
@@ -2356,10 +2340,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -2374,10 +2356,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -2392,10 +2372,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -2410,10 +2388,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -2428,10 +2404,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -2446,10 +2420,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -2464,10 +2436,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -2482,10 +2452,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -2500,10 +2468,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -2518,10 +2484,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -2536,10 +2500,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>-5.4e-05</v>
@@ -2554,10 +2516,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0.019395</v>
       </c>
       <c r="C119" s="3" t="n">
         <v>0.023872</v>
@@ -2572,10 +2532,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -2590,10 +2548,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -2608,10 +2564,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -2626,10 +2580,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -2644,10 +2596,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -2662,10 +2612,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -2680,10 +2628,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -2720,10 +2666,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>0</v>
@@ -2738,10 +2682,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0.27617</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>0.02</v>
@@ -2756,10 +2698,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.305552</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>0.218608</v>
@@ -2774,10 +2714,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0</v>
@@ -2792,10 +2730,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.08694399999999999</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>-0.199488</v>
@@ -2810,10 +2746,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.218608</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>0.018745</v>
@@ -2828,10 +2762,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -2846,10 +2778,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.382509</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.399269</v>
@@ -2869,7 +2799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3657,10 +3587,8 @@
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E25" s="5" t="n">
+        <v>-0.585838</v>
       </c>
       <c r="F25" s="5" t="n">
         <v>-0.549542</v>
@@ -3818,10 +3746,8 @@
           <t>StockBasedCompensation</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E30" s="5" t="n">
+        <v>0.103329</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3849,10 +3775,8 @@
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E31" s="5" t="n">
+        <v>0.1</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>0.169</v>
@@ -3944,10 +3868,8 @@
           <t>OperatingCashFlow</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E34" s="5" t="n">
+        <v>-0.382509</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>-0.399269</v>
@@ -3977,10 +3899,8 @@
           <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E35" s="5" t="n">
+        <v>-0.002</v>
       </c>
       <c r="F35" s="5" t="n">
         <v>-0.00795</v>
@@ -4005,11 +3925,13 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>-0.042799</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>0.027763</v>
@@ -4039,10 +3961,8 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E37" s="5" t="n">
+        <v>0.057194</v>
       </c>
       <c r="F37" s="5" t="n">
         <v>0.153288</v>
@@ -4068,10 +3988,8 @@
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E38" s="5" t="n">
+        <v>-0.363114</v>
       </c>
       <c r="F38" s="5" t="n">
         <v>-0.226168</v>
@@ -4130,10 +4048,8 @@
           <t>OperatingCashFlow</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E40" s="5" t="n">
+        <v>-0.363114</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>-0.24336</v>
@@ -4376,10 +4292,8 @@
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E48" s="5" t="n">
+        <v>0.33247</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4407,10 +4321,8 @@
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E49" s="5" t="n">
+        <v>-0.0563</v>
       </c>
       <c r="F49" s="5" t="n">
         <v>0.02</v>
@@ -4440,10 +4352,8 @@
           <t>FinancingCashFlow</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E50" s="5" t="n">
+        <v>0.27617</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>0.02</v>
@@ -4506,10 +4416,8 @@
           <t>BeginningCashPosition</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E52" s="5" t="n">
+        <v>0.305552</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>0.218608</v>
@@ -4570,10 +4478,8 @@
           <t>EndCashPosition</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E54" s="5" t="n">
+        <v>0.218608</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>0.018745</v>
@@ -4585,59 +4491,65 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures 9 $</t>
+          <t>Deferred transaction costs</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>0.278822</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0.736362</v>
+      <c r="E55" s="5" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Consulting fees 13</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net decrease in cash</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>-0.08694399999999999</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.142718</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>0.127501</v>
+        <v>-0.199488</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -4653,18 +4565,20 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Office and general</t>
+          <t>Exploration and evaluation expenditures 9 $</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" s="5" t="n">
-        <v>0.06822</v>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.063954</v>
+        <v>0.278822</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.071219</v>
+        <v>0.736362</v>
       </c>
     </row>
     <row r="58">
@@ -4680,7 +4594,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Consulting fees 13</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -4689,13 +4603,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F58" s="5" t="n">
+        <v>0.142718</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.000502</v>
+        <v>0.127501</v>
       </c>
     </row>
     <row r="59">
@@ -4711,18 +4623,18 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Office and general</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" s="5" t="n">
-        <v>0.123524</v>
+        <v>0.06822</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.042704</v>
+        <v>0.063954</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.048276</v>
+        <v>0.071219</v>
       </c>
     </row>
     <row r="60">
@@ -4738,18 +4650,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Promotion and travel</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" s="5" t="n">
-        <v>0.03241</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>0.040268</v>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.004819</v>
+        <v>0.000502</v>
       </c>
     </row>
     <row r="61">
@@ -4765,22 +4681,18 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Share-based payment 12,13</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E61" s="5" t="n">
+        <v>0.123524</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>0.042704</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.043087</v>
+        <v>0.048276</v>
       </c>
     </row>
     <row r="62">
@@ -4796,20 +4708,18 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Interest and penalties</t>
+          <t>Promotion and travel</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" s="5" t="n">
-        <v>0.003</v>
+        <v>0.03241</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.040268</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.004819</v>
       </c>
     </row>
     <row r="63">
@@ -4825,18 +4735,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Total expenses</t>
+          <t>Share-based payment 12,13</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" s="5" t="n">
-        <v>-0.585838</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>-0.569466</v>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-1.031766</v>
+        <v>0.043087</v>
       </c>
     </row>
     <row r="64">
@@ -4852,17 +4766,15 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Recovery of exploration and evaluation expenditures 6</t>
+          <t>Interest and penalties</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E64" s="5" t="n">
+        <v>0.003</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>5.4e-05</v>
+        <v>0.001</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4883,20 +4795,18 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Total expenses</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E65" s="5" t="n">
+        <v>-0.585838</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>0.001197</v>
+        <v>-0.569466</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>3e-05</v>
+        <v>-1.031766</v>
       </c>
     </row>
     <row r="66">
@@ -4912,7 +4822,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Write-off of accounts payable</t>
+          <t>Recovery of exploration and evaluation expenditures 6</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -4922,10 +4832,12 @@
         </is>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.006359</v>
-      </c>
-      <c r="G66" s="5" t="n">
-        <v>0.02546</v>
+        <v>5.4e-05</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -4941,7 +4853,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Loss on sale of the Saint Gabriel option agreement 9</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -4950,13 +4862,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F67" s="5" t="n">
+        <v>0.001197</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>-0.1665</v>
+        <v>3e-05</v>
       </c>
     </row>
     <row r="68">
@@ -4972,7 +4882,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Gain on debt settlement 12</t>
+          <t>Write-off of accounts payable</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -4982,10 +4892,10 @@
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.012314</v>
+        <v>0.006359</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.01528</v>
+        <v>0.02546</v>
       </c>
     </row>
     <row r="69">
@@ -5001,7 +4911,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Gain from disposition of investment 6</t>
+          <t>Loss on sale of the Saint Gabriel option agreement 9</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5016,7 +4926,7 @@
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.059439</v>
+        <v>-0.1665</v>
       </c>
     </row>
     <row r="70">
@@ -5032,7 +4942,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fair value adjustment on marketable securities 9</t>
+          <t>Gain on debt settlement 12</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5041,13 +4951,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F70" s="5" t="n">
+        <v>0.012314</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.012</v>
+        <v>0.01528</v>
       </c>
     </row>
     <row r="71">
@@ -5063,7 +4971,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year from discontinued operations</t>
+          <t>Gain from disposition of investment 6</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5072,11 +4980,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F71" s="5" t="n">
-        <v>-0.114931</v>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>-0.003712</v>
+        <v>0.059439</v>
       </c>
     </row>
     <row r="72">
@@ -5092,18 +5002,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
+          <t>Fair value adjustment on marketable securities 9</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" s="5" t="n">
-        <v>-0.585838</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>-0.664473</v>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-1.089769</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="73">
@@ -5119,18 +5033,20 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Shareholders of the Company</t>
+          <t>Net loss and comprehensive loss for the year from discontinued operations</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" s="5" t="n">
-        <v>-0.585838</v>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>-0.604815</v>
+        <v>-0.114931</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>-1.087936</v>
+        <v>-0.003712</v>
       </c>
     </row>
     <row r="74">
@@ -5146,20 +5062,18 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Non-controlling interests</t>
+          <t>Net loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E74" s="5" t="n">
+        <v>-0.585838</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>-0.059658</v>
+        <v>-0.664473</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-0.001833</v>
+        <v>-1.089769</v>
       </c>
     </row>
     <row r="75">
@@ -5170,25 +5084,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Continuing operations</t>
+          <t>Shareholders of the Company</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E75" s="5" t="n">
+        <v>-0.585838</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>-0.549542</v>
+        <v>-0.604815</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-1.086057</v>
+        <v>-1.087936</v>
       </c>
     </row>
     <row r="76">
@@ -5199,12 +5111,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>(1,879)          (55,273) Discontinued operations</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>(1,879)          (55,273) Discontinued operations</t>
+          <t>Non-controlling interests</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -5214,10 +5126,10 @@
         </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>-0.604815</v>
+        <v>-0.059658</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>-1.087936</v>
+        <v>-0.001833</v>
       </c>
     </row>
     <row r="77">
@@ -5228,12 +5140,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>(1,833)          (59,658) Discontinued operations</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>(1,833)          (59,658) Discontinued operations</t>
+          <t>Continuing operations</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -5243,10 +5155,10 @@
         </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>-0.059658</v>
+        <v>-0.549542</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-0.001833</v>
+        <v>-1.086057</v>
       </c>
     </row>
     <row r="78">
@@ -5257,23 +5169,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>operations</t>
+          <t>(1,879)          (55,273) Discontinued operations</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding basic and fully diluted</t>
+          <t>(1,879)          (55,273) Discontinued operations</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" s="5" t="n">
-        <v>6.35667</v>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>3.765373</v>
+        <v>-0.604815</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>10.592445</v>
+        <v>-1.087936</v>
       </c>
     </row>
     <row r="79">
@@ -5284,12 +5198,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Common                           Shares to        Reserve for       Contributed      Accumulated       Controlling</t>
+          <t>(1,833)          (59,658) Discontinued operations</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2023 3,386,377 $ 902,276 $ 2,250 $ 141,616 $ 103,329 $ (936,642) $</t>
+          <t>(1,833)          (59,658) Discontinued operations</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -5299,12 +5213,10 @@
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>0.212829</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.059658</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>-0.001833</v>
       </c>
     </row>
     <row r="80">
@@ -5315,29 +5227,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Common                           Shares to        Reserve for       Contributed      Accumulated       Controlling</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Exercise of warrants 3,750 2,250 (2,250) - - -</t>
+          <t>Weighted average number of shares outstanding basic and fully diluted</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E80" s="5" t="n">
+        <v>6.35667</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>3.765373</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>10.592445</v>
       </c>
     </row>
     <row r="81">
@@ -5353,7 +5259,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Shares issued for settlement of debts 123,146 17,241 - - - -</t>
+          <t>Balance, March 31, 2023 3,386,377 $ 902,276 $ 2,250 $ 141,616 $ 103,329 $ (936,642) $</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -5363,7 +5269,7 @@
         </is>
       </c>
       <c r="F81" s="5" t="n">
-        <v>0.017241</v>
+        <v>0.212829</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -5384,7 +5290,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Shares issued for property 650,000 169,000 - - - -</t>
+          <t>Exercise of warrants 3,750 2,250 (2,250) - - -</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -5393,8 +5299,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F82" s="5" t="n">
-        <v>0.169</v>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -5415,15 +5323,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Shares to be issued - - 20,000 - - -</t>
+          <t>Shares issued for settlement of debts 123,146 17,241 - - - -</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" s="5" t="n">
-        <v>0.02</v>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>0.02</v>
+        <v>0.017241</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5444,18 +5354,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Acquisition of Critical Foundation Metals Inc. - - - - - -</t>
+          <t>Shares issued for property 650,000 169,000 - - - -</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G84" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.169</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -5471,18 +5385,20 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Change in non-controlling interest - - - - - 64,032</t>
+          <t>Shares to be issued - - 20,000 - - -</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" s="5" t="n">
-        <v>0.1225</v>
+        <v>0.02</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>0.1225</v>
-      </c>
-      <c r="G85" s="5" t="n">
-        <v>0.058468</v>
+        <v>0.02</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -5498,18 +5414,18 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year - - - - - (604,815)</t>
+          <t>Acquisition of Critical Foundation Metals Inc. - - - - - -</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" s="5" t="n">
-        <v>-0.664473</v>
+        <v>3.1e-05</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-0.664473</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>-0.059658</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="87">
@@ -5525,20 +5441,18 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2024 4,163,273 $ 1,090,767 $ 20,000 $ 141,616 $ 103,329 $ (1,477,425) $</t>
+          <t>Change in non-controlling interest - - - - - 64,032</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E87" s="5" t="n">
+        <v>0.1225</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>-0.122872</v>
+        <v>0.1225</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>-0.001159</v>
+        <v>0.058468</v>
       </c>
     </row>
     <row r="88">
@@ -5554,22 +5468,18 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Shares issued for cash 1,500,000 150,000 (20,000) - - -</t>
+          <t>Net loss and comprehensive loss for the year - - - - - (604,815)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E88" s="5" t="n">
+        <v>-0.664473</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.664473</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>-0.059658</v>
       </c>
     </row>
     <row r="89">
@@ -5585,7 +5495,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Warrants issued in private placements - (110,776) - 110,776 - -</t>
+          <t>Balance, March 31, 2024 4,163,273 $ 1,090,767 $ 20,000 $ 141,616 $ 103,329 $ (1,477,425) $</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -5594,15 +5504,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F89" s="5" t="n">
+        <v>-0.122872</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>-0.001159</v>
       </c>
     </row>
     <row r="90">
@@ -5618,7 +5524,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Shares issued for settlement of debts 1,528,000 61,120 - - - -</t>
+          <t>Shares issued for cash 1,500,000 150,000 (20,000) - - -</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -5628,7 +5534,7 @@
         </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.06112</v>
+        <v>0.13</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -5649,7 +5555,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Shares issued for property 8,350,000 731,000 - - - -</t>
+          <t>Warrants issued in private placements - (110,776) - 110,776 - -</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -5658,8 +5564,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F91" s="5" t="n">
-        <v>0.731</v>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5680,7 +5588,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Acquisition of 1302990 BC Ltd. 2,750,000 357,500 - - - -</t>
+          <t>Shares issued for settlement of debts 1,528,000 61,120 - - - -</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -5690,7 +5598,7 @@
         </is>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.3575</v>
+        <v>0.06112</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -5711,7 +5619,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Shares to be issued - - 12,000 - - -</t>
+          <t>Shares issued for property 8,350,000 731,000 - - - -</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -5721,7 +5629,7 @@
         </is>
       </c>
       <c r="F93" s="5" t="n">
-        <v>0.012</v>
+        <v>0.731</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5742,7 +5650,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Share-based payment - - - - 43,087 -</t>
+          <t>Acquisition of 1302990 BC Ltd. 2,750,000 357,500 - - - -</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -5752,7 +5660,7 @@
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.043087</v>
+        <v>0.3575</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -5773,7 +5681,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Change in non-controlling interest - - - - - -</t>
+          <t>Shares to be issued - - 12,000 - - -</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -5783,10 +5691,12 @@
         </is>
       </c>
       <c r="F95" s="5" t="n">
-        <v>0.002992</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>0.002992</v>
+        <v>0.012</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -5802,7 +5712,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year - - - - - (1,087,936)</t>
+          <t>Share-based payment - - - - 43,087 -</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -5812,10 +5722,12 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-1.089769</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>-0.001833</v>
+        <v>0.043087</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -5831,7 +5743,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2025 18,291,273 $ 2,279,611 $ 12,000 $ 252,392 $ 146,416 $ (2,565,361) $</t>
+          <t>Change in non-controlling interest - - - - - -</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -5841,12 +5753,10 @@
         </is>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0.125058</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002992</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.002992</v>
       </c>
     </row>
     <row r="98">
@@ -5857,25 +5767,25 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Common                           Shares to        Reserve for       Contributed      Accumulated       Controlling</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures 8 $</t>
+          <t>Net loss and comprehensive loss for the year - - - - - (1,087,936)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" s="5" t="n">
-        <v>0.132207</v>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.278822</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.089769</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>-0.001833</v>
       </c>
     </row>
     <row r="99">
@@ -5886,20 +5796,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Common                           Shares to        Reserve for       Contributed      Accumulated       Controlling</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Consulting fees 11</t>
+          <t>Balance, March 31, 2025 18,291,273 $ 2,279,611 $ 12,000 $ 252,392 $ 146,416 $ (2,565,361) $</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" s="5" t="n">
-        <v>0.122872</v>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F99" s="5" t="n">
-        <v>0.142718</v>
+        <v>0.125058</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -5920,17 +5832,15 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Share-based payment 10</t>
+          <t>Exploration and evaluation expenditures 8 $</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" s="5" t="n">
-        <v>0.103329</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.132207</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>0.278822</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5951,17 +5861,15 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Part XII.6 tax</t>
+          <t>Consulting fees 11</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" s="5" t="n">
-        <v>0.000276</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.122872</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>0.142718</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5982,17 +5890,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Gain on debt settlement 10</t>
+          <t>Share-based payment 10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" s="5" t="n">
-        <v>0.012314</v>
+      <c r="E102" s="5" t="n">
+        <v>0.103329</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -6013,15 +5921,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year from continuing operations</t>
+          <t>Part XII.6 tax</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" s="5" t="n">
-        <v>-0.585838</v>
-      </c>
-      <c r="F103" s="5" t="n">
-        <v>-0.549542</v>
+        <v>0.000276</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -6037,20 +5947,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>(55,273)                     -Discontinued operations</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>(55,273)                     -Discontinued operations</t>
+          <t>Gain on debt settlement 10</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" s="5" t="n">
-        <v>-0.585838</v>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>-0.604815</v>
+        <v>0.012314</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -6066,22 +5978,20 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>(59,658)                     -Discontinued operations</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>(59,658)                     -Discontinued operations</t>
+          <t>Net loss and comprehensive loss for the year from continuing operations</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E105" s="5" t="n">
+        <v>-0.585838</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>-0.059658</v>
+        <v>-0.549542</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -6097,20 +6007,20 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>(59,658)                     -Discontinued operations</t>
+          <t>(55,273)                     -Discontinued operations</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Basic and fully diluted loss per share $</t>
+          <t>(55,273)                     -Discontinued operations</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" s="5" t="n">
-        <v>-9e-08</v>
+        <v>-0.585838</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>-8e-08</v>
+        <v>-0.604815</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -6126,20 +6036,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>operations</t>
+          <t>(59,658)                     -Discontinued operations</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Basic and fully diluted loss per share $</t>
+          <t>(59,658)                     -Discontinued operations</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" s="5" t="n">
-        <v>-9e-08</v>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F107" s="5" t="n">
-        <v>-7e-08</v>
+        <v>-0.059658</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -6155,22 +6067,20 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Common                           Shares to        Reserve for       Contributed      Accumulated       Controlling</t>
+          <t>(59,658)                     -Discontinued operations</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2022 4,051,500 $ 357,225 $ 88,800 $ 64,000 $ - $ (350,804) $</t>
+          <t>Basic and fully diluted loss per share $</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" s="5" t="n">
-        <v>0.159221</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-9e-08</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>-8e-08</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -6186,22 +6096,20 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Common                           Shares to        Reserve for       Contributed      Accumulated       Controlling</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Shares issued for cash 1,260,280 339,266 (56,300) - - -</t>
+          <t>Basic and fully diluted loss per share $</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" s="5" t="n">
-        <v>0.282966</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-9e-08</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>-7e-08</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6222,14 +6130,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Warrants issued in private placements - (77,616) - 77,616 - -</t>
+          <t>Balance, March 31, 2022 4,051,500 $ 357,225 $ 88,800 $ 64,000 $ - $ (350,804) $</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E110" s="5" t="n">
+        <v>0.159221</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -6255,12 +6161,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Exercise of warrants 10,000 3,000 - - - -</t>
+          <t>Shares issued for cash 1,260,280 339,266 (56,300) - - -</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" s="5" t="n">
-        <v>0.003</v>
+        <v>0.282966</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -6286,12 +6192,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Shares issued for settlement of debts 950,985 190,197 (30,250) - - -</t>
+          <t>Warrants issued in private placements - (77,616) - 77,616 - -</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" s="5" t="n">
-        <v>0.159947</v>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -6317,12 +6225,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Shares issued for property 500,000 100,000 - - - -</t>
+          <t>Exercise of warrants 10,000 3,000 - - - -</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" s="5" t="n">
-        <v>0.1</v>
+        <v>0.003</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -6348,12 +6256,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Share-based payment - - - - 103,329 -</t>
+          <t>Shares issued for settlement of debts 950,985 190,197 (30,250) - - -</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" s="5" t="n">
-        <v>0.103329</v>
+        <v>0.159947</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -6379,12 +6287,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Share issue costs - (9,796) - - - -</t>
+          <t>Shares issued for property 500,000 100,000 - - - -</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" s="5" t="n">
-        <v>-0.009795999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -6410,12 +6318,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year - - - - (585,838)</t>
+          <t>Share-based payment - - - - 103,329 -</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" s="5" t="n">
-        <v>-0.585838</v>
+        <v>0.103329</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -6441,12 +6349,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2023 6,772,765 $ 902,276 $ 2,250 $ 141,616 $ 103,329 $ (936,642) $</t>
+          <t>Share issue costs - (9,796) - - - -</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" s="5" t="n">
-        <v>0.212829</v>
+        <v>-0.009795999999999999</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -6472,14 +6380,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Exercise of warrants 7,500 2,250 (2,250) - - -</t>
+          <t>Net loss and comprehensive loss for the year - - - - (585,838)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E118" s="5" t="n">
+        <v>-0.585838</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -6505,12 +6411,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Shares issued for settlement of debts 246,292 17,241 - - - -</t>
+          <t>Balance, March 31, 2023 6,772,765 $ 902,276 $ 2,250 $ 141,616 $ 103,329 $ (936,642) $</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" s="5" t="n">
-        <v>0.017241</v>
+        <v>0.212829</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -6536,12 +6442,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Shares issued for property 1,300,000 169,000 - - - -</t>
+          <t>Exercise of warrants 7,500 2,250 (2,250) - - -</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
-      <c r="E120" s="5" t="n">
-        <v>0.169</v>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -6567,17 +6475,79 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2024 8,326,557 $ 1,090,767 $ 20,000 $ 141,616 $ 103,329 $ (1,477,425) $</t>
+          <t>Shares issued for settlement of debts 246,292 17,241 - - - -</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" s="5" t="n">
+        <v>0.017241</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Common                           Shares to        Reserve for       Contributed      Accumulated       Controlling</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Shares issued for property 1,300,000 169,000 - - - -</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" s="5" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Common                           Shares to        Reserve for       Contributed      Accumulated       Controlling</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Balance, March 31, 2024 8,326,557 $ 1,090,767 $ 20,000 $ 141,616 $ 103,329 $ (1,477,425) $</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" s="5" t="n">
         <v>-0.122872</v>
       </c>
-      <c r="F121" s="5" t="n">
+      <c r="F123" s="5" t="n">
         <v>-0.001159</v>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t>-</t>
         </is>
